--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/7631-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/7631-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50A0059D-E955-4DB4-AA49-529F1E08B1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9106383-90E5-4F2C-BA6E-487C0865C8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{075236A4-8997-4AFA-A3DC-12B3103B181B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{848F5A12-B9DC-4CB1-BCE8-A4D1E60D39E5}"/>
   </bookViews>
   <sheets>
     <sheet name="7631-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1534,25 +1534,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B3238C3-4792-4F70-9BFD-534D7237FE38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9882BE-68FF-4B16-9F2F-0AE293728074}">
   <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1706,7 +1706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1786,7 +1786,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="49">
         <v>2023</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>27</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51" t="s">
         <v>49</v>
       </c>
